--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,6 +898,44 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>475150</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7088291</v>
+      </c>
+      <c r="E13" t="n">
+        <v>55900</v>
+      </c>
+      <c r="F13" t="n">
+        <v>396235.4669</v>
+      </c>
+      <c r="G13" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>136.86</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>건물 건설업</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,6 +936,44 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>475150</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13246218</v>
+      </c>
+      <c r="E14" t="n">
+        <v>62000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>821265.5159999999</v>
+      </c>
+      <c r="G14" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>173.73</v>
+      </c>
+      <c r="I14" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>건물 건설업</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,6 +974,82 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>475150</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>18259402</v>
+      </c>
+      <c r="E15" t="n">
+        <v>80600</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1471707.8012</v>
+      </c>
+      <c r="G15" t="n">
+        <v>80</v>
+      </c>
+      <c r="H15" t="n">
+        <v>253.51</v>
+      </c>
+      <c r="I15" t="n">
+        <v>30</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>건물 건설업</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1010682</v>
+      </c>
+      <c r="E16" t="n">
+        <v>93600</v>
+      </c>
+      <c r="F16" t="n">
+        <v>94599.8352</v>
+      </c>
+      <c r="G16" t="n">
+        <v>51</v>
+      </c>
+      <c r="H16" t="n">
+        <v>79.65000000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1050,6 +1050,120 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>475150</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>20815136</v>
+      </c>
+      <c r="E17" t="n">
+        <v>80900</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1683944.5024</v>
+      </c>
+      <c r="G17" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>259.56</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>건물 건설업</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>978445</v>
+      </c>
+      <c r="E18" t="n">
+        <v>95300</v>
+      </c>
+      <c r="F18" t="n">
+        <v>93245.8085</v>
+      </c>
+      <c r="G18" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>578041</v>
+      </c>
+      <c r="E19" t="n">
+        <v>151200</v>
+      </c>
+      <c r="F19" t="n">
+        <v>87399.79919999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>138.86</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,6 +1164,44 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>105560</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1297500</v>
+      </c>
+      <c r="E20" t="n">
+        <v>165200</v>
+      </c>
+      <c r="F20" t="n">
+        <v>214347</v>
+      </c>
+      <c r="G20" t="n">
+        <v>50</v>
+      </c>
+      <c r="H20" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1462,6 +1462,206 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>105560</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1676652</v>
+      </c>
+      <c r="E21" t="n">
+        <v>167400</v>
+      </c>
+      <c r="F21" t="n">
+        <v>280671.5448</v>
+      </c>
+      <c r="G21" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>55550</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>신한지주</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1471472</v>
+      </c>
+      <c r="E22" t="n">
+        <v>100800</v>
+      </c>
+      <c r="F22" t="n">
+        <v>148324.3776</v>
+      </c>
+      <c r="G22" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>33780</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>KT&amp;G</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>355648</v>
+      </c>
+      <c r="E23" t="n">
+        <v>185800</v>
+      </c>
+      <c r="F23" t="n">
+        <v>66079.39840000001</v>
+      </c>
+      <c r="G23" t="n">
+        <v>51</v>
+      </c>
+      <c r="H23" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>담배 제조업</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>647795</v>
+      </c>
+      <c r="E24" t="n">
+        <v>86500</v>
+      </c>
+      <c r="F24" t="n">
+        <v>56034.2675</v>
+      </c>
+      <c r="G24" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>63.52</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1662,6 +1662,106 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>105560</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1508044</v>
+      </c>
+      <c r="E25" t="n">
+        <v>168500</v>
+      </c>
+      <c r="F25" t="n">
+        <v>254105.414</v>
+      </c>
+      <c r="G25" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>871008</v>
+      </c>
+      <c r="E26" t="n">
+        <v>89000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>77519.712</v>
+      </c>
+      <c r="G26" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>71.81</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1762,6 +1762,106 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>105560</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1508057</v>
+      </c>
+      <c r="E27" t="n">
+        <v>168500</v>
+      </c>
+      <c r="F27" t="n">
+        <v>254107.6045</v>
+      </c>
+      <c r="G27" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>871059</v>
+      </c>
+      <c r="E28" t="n">
+        <v>89000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>77524.251</v>
+      </c>
+      <c r="G28" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>71.81</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1862,6 +1862,57 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>756290</v>
+      </c>
+      <c r="E29" t="n">
+        <v>96900</v>
+      </c>
+      <c r="F29" t="n">
+        <v>73284.501</v>
+      </c>
+      <c r="G29" t="n">
+        <v>61</v>
+      </c>
+      <c r="H29" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="I29" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1913,6 +1913,57 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>6340</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>대원전선</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>43105805</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15450</v>
+      </c>
+      <c r="F30" t="n">
+        <v>665984.68725</v>
+      </c>
+      <c r="G30" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>443.06</v>
+      </c>
+      <c r="I30" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1964,6 +1964,108 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>41830</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>인바디</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>654568</v>
+      </c>
+      <c r="E31" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F31" t="n">
+        <v>45819.76</v>
+      </c>
+      <c r="G31" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="I31" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>의료용 기기 제조업</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>144960</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3348145</v>
+      </c>
+      <c r="E32" t="n">
+        <v>10980</v>
+      </c>
+      <c r="F32" t="n">
+        <v>36762.6321</v>
+      </c>
+      <c r="G32" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>99.27</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2066,6 +2066,106 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>55550</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>신한지주</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1389170</v>
+      </c>
+      <c r="E33" t="n">
+        <v>110000</v>
+      </c>
+      <c r="F33" t="n">
+        <v>152808.7</v>
+      </c>
+      <c r="G33" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>63.69</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>569838</v>
+      </c>
+      <c r="E34" t="n">
+        <v>137600</v>
+      </c>
+      <c r="F34" t="n">
+        <v>78409.70879999999</v>
+      </c>
+      <c r="G34" t="n">
+        <v>68</v>
+      </c>
+      <c r="H34" t="n">
+        <v>121.22</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2166,6 +2166,155 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>55550</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>신한지주</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1389243</v>
+      </c>
+      <c r="E35" t="n">
+        <v>110000</v>
+      </c>
+      <c r="F35" t="n">
+        <v>152816.73</v>
+      </c>
+      <c r="G35" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>63.69</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>569842</v>
+      </c>
+      <c r="E36" t="n">
+        <v>137600</v>
+      </c>
+      <c r="F36" t="n">
+        <v>78410.2592</v>
+      </c>
+      <c r="G36" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>121.22</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>86790</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>하나금융지주</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>578150</v>
+      </c>
+      <c r="E37" t="n">
+        <v>134700</v>
+      </c>
+      <c r="F37" t="n">
+        <v>77876.80499999999</v>
+      </c>
+      <c r="G37" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2166,155 +2166,6 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>55550</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>신한지주</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1389243</v>
-      </c>
-      <c r="E35" t="n">
-        <v>110000</v>
-      </c>
-      <c r="F35" t="n">
-        <v>152816.73</v>
-      </c>
-      <c r="G35" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="H35" t="n">
-        <v>63.69</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>기타 금융업</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>금융</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>10950</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>S-Oil</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>569842</v>
-      </c>
-      <c r="E36" t="n">
-        <v>137600</v>
-      </c>
-      <c r="F36" t="n">
-        <v>78410.2592</v>
-      </c>
-      <c r="G36" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="H36" t="n">
-        <v>121.22</v>
-      </c>
-      <c r="I36" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>석유 정제품 제조업</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>86790</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>하나금융지주</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>578150</v>
-      </c>
-      <c r="E37" t="n">
-        <v>134700</v>
-      </c>
-      <c r="F37" t="n">
-        <v>77876.80499999999</v>
-      </c>
-      <c r="G37" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>기타 금융업</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>금융</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2166,6 +2166,310 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>6360</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4877996</v>
+      </c>
+      <c r="E35" t="n">
+        <v>34900</v>
+      </c>
+      <c r="F35" t="n">
+        <v>170242.0604</v>
+      </c>
+      <c r="G35" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>72.77</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>건물 건설업</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>181710</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NHN</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1282545</v>
+      </c>
+      <c r="E36" t="n">
+        <v>54200</v>
+      </c>
+      <c r="F36" t="n">
+        <v>69513.939</v>
+      </c>
+      <c r="G36" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>88.84999999999999</v>
+      </c>
+      <c r="I36" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>403728</v>
+      </c>
+      <c r="E37" t="n">
+        <v>141600</v>
+      </c>
+      <c r="F37" t="n">
+        <v>57167.8848</v>
+      </c>
+      <c r="G37" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>124.05</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>현대해상</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1148157</v>
+      </c>
+      <c r="E38" t="n">
+        <v>44050</v>
+      </c>
+      <c r="F38" t="n">
+        <v>50576.31585</v>
+      </c>
+      <c r="G38" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="I38" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>보험업</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>185634</v>
+      </c>
+      <c r="E39" t="n">
+        <v>244500</v>
+      </c>
+      <c r="F39" t="n">
+        <v>45387.513</v>
+      </c>
+      <c r="G39" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="H39" t="n">
+        <v>528.53</v>
+      </c>
+      <c r="I39" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>452290</v>
+      </c>
+      <c r="E40" t="n">
+        <v>97500</v>
+      </c>
+      <c r="F40" t="n">
+        <v>44098.275</v>
+      </c>
+      <c r="G40" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>95.98</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2470,6 +2470,261 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>6340</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>대원전선</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>26184084</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16030</v>
+      </c>
+      <c r="F41" t="n">
+        <v>419730.86652</v>
+      </c>
+      <c r="G41" t="n">
+        <v>92</v>
+      </c>
+      <c r="H41" t="n">
+        <v>448.03</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2990</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>21097524</v>
+      </c>
+      <c r="E42" t="n">
+        <v>14930</v>
+      </c>
+      <c r="F42" t="n">
+        <v>314986.03332</v>
+      </c>
+      <c r="G42" t="n">
+        <v>86</v>
+      </c>
+      <c r="H42" t="n">
+        <v>335.91</v>
+      </c>
+      <c r="I42" t="n">
+        <v>29.94</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>건물 건설업</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>278470</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>에이피알</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>392349</v>
+      </c>
+      <c r="E43" t="n">
+        <v>397000</v>
+      </c>
+      <c r="F43" t="n">
+        <v>155762.553</v>
+      </c>
+      <c r="G43" t="n">
+        <v>64</v>
+      </c>
+      <c r="H43" t="n">
+        <v>116.11</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>기타 화학제품 제조업</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>123</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>827907</v>
+      </c>
+      <c r="E44" t="n">
+        <v>101000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>83618.607</v>
+      </c>
+      <c r="G44" t="n">
+        <v>60</v>
+      </c>
+      <c r="H44" t="n">
+        <v>104.87</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>181710</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NHN</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1258303</v>
+      </c>
+      <c r="E45" t="n">
+        <v>61300</v>
+      </c>
+      <c r="F45" t="n">
+        <v>77133.9739</v>
+      </c>
+      <c r="G45" t="n">
+        <v>63</v>
+      </c>
+      <c r="H45" t="n">
+        <v>113.59</v>
+      </c>
+      <c r="I45" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2725,6 +2725,210 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>278470</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>에이피알</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>298745</v>
+      </c>
+      <c r="E46" t="n">
+        <v>399500</v>
+      </c>
+      <c r="F46" t="n">
+        <v>119348.6275</v>
+      </c>
+      <c r="G46" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>132.27</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>기타 화학제품 제조업</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>123</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>941758</v>
+      </c>
+      <c r="E47" t="n">
+        <v>107400</v>
+      </c>
+      <c r="F47" t="n">
+        <v>101144.8092</v>
+      </c>
+      <c r="G47" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>129.49</v>
+      </c>
+      <c r="I47" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>181710</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NHN</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>853857</v>
+      </c>
+      <c r="E48" t="n">
+        <v>66700</v>
+      </c>
+      <c r="F48" t="n">
+        <v>56952.2619</v>
+      </c>
+      <c r="G48" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="I48" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>144960</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3166800</v>
+      </c>
+      <c r="E49" t="n">
+        <v>12490</v>
+      </c>
+      <c r="F49" t="n">
+        <v>39553.332</v>
+      </c>
+      <c r="G49" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>133.46</v>
+      </c>
+      <c r="I49" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>특수 목적용 기계 제조업</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2929,6 +2929,157 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5935</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3841053</v>
+      </c>
+      <c r="E50" t="n">
+        <v>195600</v>
+      </c>
+      <c r="F50" t="n">
+        <v>751309.9668000001</v>
+      </c>
+      <c r="G50" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="H50" t="n">
+        <v>243.76</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>804594</v>
+      </c>
+      <c r="E51" t="n">
+        <v>117000</v>
+      </c>
+      <c r="F51" t="n">
+        <v>94137.49800000001</v>
+      </c>
+      <c r="G51" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="H51" t="n">
+        <v>146.06</v>
+      </c>
+      <c r="I51" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>325864</v>
+      </c>
+      <c r="E52" t="n">
+        <v>147600</v>
+      </c>
+      <c r="F52" t="n">
+        <v>48097.5264</v>
+      </c>
+      <c r="G52" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="H52" t="n">
+        <v>147.24</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3080,6 +3080,259 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>현대해상</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1420111</v>
+      </c>
+      <c r="E53" t="n">
+        <v>49700</v>
+      </c>
+      <c r="F53" t="n">
+        <v>70579.51669999999</v>
+      </c>
+      <c r="G53" t="n">
+        <v>58</v>
+      </c>
+      <c r="H53" t="n">
+        <v>87.19</v>
+      </c>
+      <c r="I53" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>보험업</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>450805</v>
+      </c>
+      <c r="E54" t="n">
+        <v>153600</v>
+      </c>
+      <c r="F54" t="n">
+        <v>69243.648</v>
+      </c>
+      <c r="G54" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="H54" t="n">
+        <v>152.63</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>7340</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DN오토모티브</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>974624</v>
+      </c>
+      <c r="E55" t="n">
+        <v>62800</v>
+      </c>
+      <c r="F55" t="n">
+        <v>61206.3872</v>
+      </c>
+      <c r="G55" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>137.88</v>
+      </c>
+      <c r="I55" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>일차전지 및 이차전지 제조업</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>184421</v>
+      </c>
+      <c r="E56" t="n">
+        <v>269000</v>
+      </c>
+      <c r="F56" t="n">
+        <v>49609.249</v>
+      </c>
+      <c r="G56" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>610.7</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>5950</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>이수화학</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2312968</v>
+      </c>
+      <c r="E57" t="n">
+        <v>13570</v>
+      </c>
+      <c r="F57" t="n">
+        <v>31386.97576</v>
+      </c>
+      <c r="G57" t="n">
+        <v>65</v>
+      </c>
+      <c r="H57" t="n">
+        <v>120.65</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-13.29</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>기초 화학물질 제조업</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3333,6 +3333,208 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>6360</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2835555</v>
+      </c>
+      <c r="E58" t="n">
+        <v>34950</v>
+      </c>
+      <c r="F58" t="n">
+        <v>99102.64724999999</v>
+      </c>
+      <c r="G58" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="H58" t="n">
+        <v>78.86</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>건물 건설업</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>345748</v>
+      </c>
+      <c r="E59" t="n">
+        <v>151600</v>
+      </c>
+      <c r="F59" t="n">
+        <v>52415.3968</v>
+      </c>
+      <c r="G59" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>142.95</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>현대해상</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1009478</v>
+      </c>
+      <c r="E60" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F60" t="n">
+        <v>50473.9</v>
+      </c>
+      <c r="G60" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="H60" t="n">
+        <v>85.87</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>보험업</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>145522</v>
+      </c>
+      <c r="E61" t="n">
+        <v>256000</v>
+      </c>
+      <c r="F61" t="n">
+        <v>37253.632</v>
+      </c>
+      <c r="G61" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="H61" t="n">
+        <v>571.04</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-4.83</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3535,6 +3535,159 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2990</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>25656110</v>
+      </c>
+      <c r="E62" t="n">
+        <v>15650</v>
+      </c>
+      <c r="F62" t="n">
+        <v>401518.1215</v>
+      </c>
+      <c r="G62" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>344.6</v>
+      </c>
+      <c r="I62" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>건물 건설업</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>278470</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>에이피알</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>332431</v>
+      </c>
+      <c r="E63" t="n">
+        <v>386000</v>
+      </c>
+      <c r="F63" t="n">
+        <v>128318.366</v>
+      </c>
+      <c r="G63" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="H63" t="n">
+        <v>75.84999999999999</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>기타 화학제품 제조업</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>123</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>149982</v>
+      </c>
+      <c r="E64" t="n">
+        <v>242000</v>
+      </c>
+      <c r="F64" t="n">
+        <v>36295.644</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="H64" t="n">
+        <v>521.3099999999999</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3688,6 +3688,106 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>5935</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10328436</v>
+      </c>
+      <c r="E65" t="n">
+        <v>207000</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2137986.252</v>
+      </c>
+      <c r="G65" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>254.45</v>
+      </c>
+      <c r="I65" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2990</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>31297012</v>
+      </c>
+      <c r="E66" t="n">
+        <v>14750</v>
+      </c>
+      <c r="F66" t="n">
+        <v>461630.927</v>
+      </c>
+      <c r="G66" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="H66" t="n">
+        <v>323.24</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>건물 건설업</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +3788,57 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>278470</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>에이피알</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>358052</v>
+      </c>
+      <c r="E67" t="n">
+        <v>409500</v>
+      </c>
+      <c r="F67" t="n">
+        <v>146622.294</v>
+      </c>
+      <c r="G67" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>81.19</v>
+      </c>
+      <c r="I67" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>기타 화학제품 제조업</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>123</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3839,6 +3839,210 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>278470</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>에이피알</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>453936</v>
+      </c>
+      <c r="E68" t="n">
+        <v>440500</v>
+      </c>
+      <c r="F68" t="n">
+        <v>199958.808</v>
+      </c>
+      <c r="G68" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H68" t="n">
+        <v>100.68</v>
+      </c>
+      <c r="I68" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>기타 화학제품 제조업</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>123</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>614418</v>
+      </c>
+      <c r="E69" t="n">
+        <v>121800</v>
+      </c>
+      <c r="F69" t="n">
+        <v>74836.1124</v>
+      </c>
+      <c r="G69" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="H69" t="n">
+        <v>162.78</v>
+      </c>
+      <c r="I69" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>161890</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>470503</v>
+      </c>
+      <c r="E70" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F70" t="n">
+        <v>70575.45</v>
+      </c>
+      <c r="G70" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I70" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>기타 화학제품 제조업</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>28670</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>팬오션</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>6430072</v>
+      </c>
+      <c r="E71" t="n">
+        <v>6380</v>
+      </c>
+      <c r="F71" t="n">
+        <v>41023.85936</v>
+      </c>
+      <c r="G71" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="H71" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>해상 운송업</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4043,6 +4043,159 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>6360</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>5379779</v>
+      </c>
+      <c r="E72" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F72" t="n">
+        <v>203355.6462</v>
+      </c>
+      <c r="G72" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="H72" t="n">
+        <v>103.88</v>
+      </c>
+      <c r="I72" t="n">
+        <v>8</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>건물 건설업</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>659460</v>
+      </c>
+      <c r="E73" t="n">
+        <v>127700</v>
+      </c>
+      <c r="F73" t="n">
+        <v>84213.042</v>
+      </c>
+      <c r="G73" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="H73" t="n">
+        <v>174.03</v>
+      </c>
+      <c r="I73" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>477621</v>
+      </c>
+      <c r="E74" t="n">
+        <v>141000</v>
+      </c>
+      <c r="F74" t="n">
+        <v>67344.561</v>
+      </c>
+      <c r="G74" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="H74" t="n">
+        <v>129.27</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4196,6 +4196,108 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>222800</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1716440</v>
+      </c>
+      <c r="E75" t="n">
+        <v>126900</v>
+      </c>
+      <c r="F75" t="n">
+        <v>217816.236</v>
+      </c>
+      <c r="G75" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="H75" t="n">
+        <v>407.6</v>
+      </c>
+      <c r="I75" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>402317</v>
+      </c>
+      <c r="E76" t="n">
+        <v>136700</v>
+      </c>
+      <c r="F76" t="n">
+        <v>54996.7339</v>
+      </c>
+      <c r="G76" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>123.37</v>
+      </c>
+      <c r="I76" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4298,6 +4298,306 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2990</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>18306693</v>
+      </c>
+      <c r="E77" t="n">
+        <v>16460</v>
+      </c>
+      <c r="F77" t="n">
+        <v>301328.16678</v>
+      </c>
+      <c r="G77" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="H77" t="n">
+        <v>308.94</v>
+      </c>
+      <c r="I77" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>건물 건설업</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>86790</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>하나금융지주</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1316768</v>
+      </c>
+      <c r="E78" t="n">
+        <v>136300</v>
+      </c>
+      <c r="F78" t="n">
+        <v>179475.4784</v>
+      </c>
+      <c r="G78" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="H78" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>609124</v>
+      </c>
+      <c r="E79" t="n">
+        <v>150100</v>
+      </c>
+      <c r="F79" t="n">
+        <v>91429.51240000001</v>
+      </c>
+      <c r="G79" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>144.46</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>161890</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>434278</v>
+      </c>
+      <c r="E80" t="n">
+        <v>160100</v>
+      </c>
+      <c r="F80" t="n">
+        <v>69527.9078</v>
+      </c>
+      <c r="G80" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H80" t="n">
+        <v>102.66</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>기타 화학제품 제조업</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>88350</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>4843882</v>
+      </c>
+      <c r="E81" t="n">
+        <v>5770</v>
+      </c>
+      <c r="F81" t="n">
+        <v>27949.19914</v>
+      </c>
+      <c r="G81" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>84.94</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>보험업</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>현대해상</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>498068</v>
+      </c>
+      <c r="E82" t="n">
+        <v>50900</v>
+      </c>
+      <c r="F82" t="n">
+        <v>25351.6612</v>
+      </c>
+      <c r="G82" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="H82" t="n">
+        <v>78.91</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>보험업</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4598,6 +4598,57 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>161890</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>392181</v>
+      </c>
+      <c r="E83" t="n">
+        <v>155000</v>
+      </c>
+      <c r="F83" t="n">
+        <v>60788.055</v>
+      </c>
+      <c r="G83" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="H83" t="n">
+        <v>95.45999999999999</v>
+      </c>
+      <c r="I83" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>기타 화학제품 제조업</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4649,6 +4649,57 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2990</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>20120393</v>
+      </c>
+      <c r="E84" t="n">
+        <v>17100</v>
+      </c>
+      <c r="F84" t="n">
+        <v>344058.7203</v>
+      </c>
+      <c r="G84" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="H84" t="n">
+        <v>322.22</v>
+      </c>
+      <c r="I84" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>건물 건설업</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4700,6 +4700,104 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>88350</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>22315917</v>
+      </c>
+      <c r="E85" t="n">
+        <v>6110</v>
+      </c>
+      <c r="F85" t="n">
+        <v>136350.25287</v>
+      </c>
+      <c r="G85" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="H85" t="n">
+        <v>98.06</v>
+      </c>
+      <c r="I85" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>보험업</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>810</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>삼성화재</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>168944</v>
+      </c>
+      <c r="E86" t="n">
+        <v>702000</v>
+      </c>
+      <c r="F86" t="n">
+        <v>118598.688</v>
+      </c>
+      <c r="G86" t="n">
+        <v>50</v>
+      </c>
+      <c r="H86" t="n">
+        <v>58.47</v>
+      </c>
+      <c r="I86" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>보험업</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4798,6 +4798,108 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>918696</v>
+      </c>
+      <c r="E87" t="n">
+        <v>157300</v>
+      </c>
+      <c r="F87" t="n">
+        <v>144510.8808</v>
+      </c>
+      <c r="G87" t="n">
+        <v>62</v>
+      </c>
+      <c r="H87" t="n">
+        <v>158.72</v>
+      </c>
+      <c r="I87" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>석유 정제품 제조업</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>506909</v>
+      </c>
+      <c r="E88" t="n">
+        <v>123900</v>
+      </c>
+      <c r="F88" t="n">
+        <v>62806.0251</v>
+      </c>
+      <c r="G88" t="n">
+        <v>66</v>
+      </c>
+      <c r="H88" t="n">
+        <v>178.43</v>
+      </c>
+      <c r="I88" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4900,6 +4900,55 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>5935</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>3114157</v>
+      </c>
+      <c r="E89" t="n">
+        <v>199600</v>
+      </c>
+      <c r="F89" t="n">
+        <v>621585.7372</v>
+      </c>
+      <c r="G89" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="H89" t="n">
+        <v>247.13</v>
+      </c>
+      <c r="I89" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>에너지장비및서비스</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -631,7 +631,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -784,7 +784,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>기타 금속 가공제품 제조업</t>
+          <t>기계</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -835,7 +835,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>에너지장비및서비스</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -988,7 +988,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>에너지장비및서비스</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>에너지장비및서비스</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>에너지장비및서비스</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>에너지장비및서비스</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>담배 제조업</t>
+          <t>담배</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>전기장비</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>건강관리장비와용품</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>IT서비스</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>손해보험</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>전기장비</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>IT서비스</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>IT서비스</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>손해보험</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>일차전지 및 이차전지 제조업</t>
+          <t>자동차부품</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>손해보험</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>해상 운송업</t>
+          <t>해운사</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>전자장비와기기</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>생명보험</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>손해보험</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>건물 건설업</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>생명보험</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>보험업</t>
+          <t>손해보험</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>석유 정제품 제조업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>석유와가스</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>반도체와반도체장비</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -4946,6 +4946,261 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>500</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>685340</v>
+      </c>
+      <c r="E90" t="n">
+        <v>265500</v>
+      </c>
+      <c r="F90" t="n">
+        <v>181957.77</v>
+      </c>
+      <c r="G90" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="H90" t="n">
+        <v>688.4400000000001</v>
+      </c>
+      <c r="I90" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>전기장비</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>222800</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>844161</v>
+      </c>
+      <c r="E91" t="n">
+        <v>132600</v>
+      </c>
+      <c r="F91" t="n">
+        <v>111935.7486</v>
+      </c>
+      <c r="G91" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="H91" t="n">
+        <v>410</v>
+      </c>
+      <c r="I91" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>전자장비와기기</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>51</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>562109</v>
+      </c>
+      <c r="E92" t="n">
+        <v>165900</v>
+      </c>
+      <c r="F92" t="n">
+        <v>93253.88310000001</v>
+      </c>
+      <c r="G92" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="H92" t="n">
+        <v>173.76</v>
+      </c>
+      <c r="I92" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>652694</v>
+      </c>
+      <c r="E93" t="n">
+        <v>122100</v>
+      </c>
+      <c r="F93" t="n">
+        <v>79693.9374</v>
+      </c>
+      <c r="G93" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="H93" t="n">
+        <v>165.43</v>
+      </c>
+      <c r="I93" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>6360</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1641254</v>
+      </c>
+      <c r="E94" t="n">
+        <v>35550</v>
+      </c>
+      <c r="F94" t="n">
+        <v>58346.5797</v>
+      </c>
+      <c r="G94" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="H94" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>

--- a/종목탐색_TOP30.xlsx
+++ b/종목탐색_TOP30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5204,6 +5204,512 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>36930</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>5046931</v>
+      </c>
+      <c r="E95" t="n">
+        <v>221000</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1115371.751</v>
+      </c>
+      <c r="G95" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="H95" t="n">
+        <v>706.5700000000001</v>
+      </c>
+      <c r="I95" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>5935</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>3459475</v>
+      </c>
+      <c r="E96" t="n">
+        <v>203000</v>
+      </c>
+      <c r="F96" t="n">
+        <v>702273.425</v>
+      </c>
+      <c r="G96" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="H96" t="n">
+        <v>258.66</v>
+      </c>
+      <c r="I96" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>222800</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1830166</v>
+      </c>
+      <c r="E97" t="n">
+        <v>133900</v>
+      </c>
+      <c r="F97" t="n">
+        <v>245059.2274</v>
+      </c>
+      <c r="G97" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="H97" t="n">
+        <v>425.1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>전자장비와기기</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>51</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>131290</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>796012</v>
+      </c>
+      <c r="E98" t="n">
+        <v>306500</v>
+      </c>
+      <c r="F98" t="n">
+        <v>243977.678</v>
+      </c>
+      <c r="G98" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="H98" t="n">
+        <v>716.25</v>
+      </c>
+      <c r="I98" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1055733</v>
+      </c>
+      <c r="E99" t="n">
+        <v>154900</v>
+      </c>
+      <c r="F99" t="n">
+        <v>163533.0417</v>
+      </c>
+      <c r="G99" t="n">
+        <v>74</v>
+      </c>
+      <c r="H99" t="n">
+        <v>156.88</v>
+      </c>
+      <c r="I99" t="n">
+        <v>-6.63</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>55550</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>신한지주</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1398304</v>
+      </c>
+      <c r="E100" t="n">
+        <v>110300</v>
+      </c>
+      <c r="F100" t="n">
+        <v>154232.9312</v>
+      </c>
+      <c r="G100" t="n">
+        <v>50</v>
+      </c>
+      <c r="H100" t="n">
+        <v>68.91</v>
+      </c>
+      <c r="I100" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>은행</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>78930</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>858130</v>
+      </c>
+      <c r="E101" t="n">
+        <v>117900</v>
+      </c>
+      <c r="F101" t="n">
+        <v>101173.527</v>
+      </c>
+      <c r="G101" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="H101" t="n">
+        <v>159.12</v>
+      </c>
+      <c r="I101" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>석유와가스</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>31980</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>519773</v>
+      </c>
+      <c r="E102" t="n">
+        <v>155000</v>
+      </c>
+      <c r="F102" t="n">
+        <v>80564.815</v>
+      </c>
+      <c r="G102" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="H102" t="n">
+        <v>351.9</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>6360</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1711088</v>
+      </c>
+      <c r="E103" t="n">
+        <v>37250</v>
+      </c>
+      <c r="F103" t="n">
+        <v>63738.028</v>
+      </c>
+      <c r="G103" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="H103" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="I103" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>161890</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>320303</v>
+      </c>
+      <c r="E104" t="n">
+        <v>139400</v>
+      </c>
+      <c r="F104" t="n">
+        <v>44650.2382</v>
+      </c>
+      <c r="G104" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="I104" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
